--- a/stories/arbres/TREE-SAN-020.xlsx
+++ b/stories/arbres/TREE-SAN-020.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va au parc avec papa. Maman porte le panier. C'est l'heure de manger. On s'assoit. Assis à table, ensemble. Ici, la table est une nappe. Noé pose les fesses.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Le matin, l'herbe est fraîche. Papa étend la nappe. Noé s'assoit. Les fesses sur la nappe. Maman s'assoit. Ils mangent ensemble, à table. Noé reste assis.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1857,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va manger. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2030,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Noé est assis. Le matin, à table, ensemble. La nappe est leur table.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2181,6 +2223,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -2345,6 +2392,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose le ballon rouge. Il s'assoit. À table, ensemble. Papa coupe le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2585,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2754,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'assoit près de Noé. Ils mangent assis à table, ensemble. Le matin. Le ballon rouge attend.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2921,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3088,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'assoit. Noé est assis à table, ensemble. Le matin. Une miette tombe.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3255,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3422,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'assoit. Noé reste assis. À table, ensemble. Le matin. Papa coupe le pain.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3589,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3756,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose le seau bleu. Il s'assoit. À table, ensemble. Maman verse de l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3949,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4118,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'assoit. Noé est assis à table, ensemble. Le matin. Maman verse de l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4285,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4452,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'assoit tout doux. Noé reste assis. À table, ensemble. Le seau bleu est posé.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4619,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4786,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sami pose le seau. Noé est assis à table, ensemble. Le matin, l'herbe est fraîche.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4953,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4855,7 +4982,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Noé pose le doudou. Il s'assoit. À table, ensemble. Papa dit : bien.</t>
+          <t>Noé pose le doudou. Il s'assoit. À table, ensemble. Bien.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -4993,6 +5120,12 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose le doudou. Il s'assoit. À table, ensemble.
+papa|Bien.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5314,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5483,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'assoit. Le doudou aussi, à sa place. Noé est assis à table, ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5650,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5531,7 +5679,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Léa sourit. Noé est assis à table, ensemble. Le matin. Papa dit : bien.</t>
+          <t>Léa sourit. Noé est assis à table, ensemble. Le matin. Bien.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5669,6 +5817,12 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Léa sourit. Noé est assis à table, ensemble. Le matin.
+papa|Bien.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5985,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6152,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sami tapote le doudou. Noé reste assis. À table, ensemble. Une abeille passe loin.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6319,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6317,6 +6486,11 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Noé a faim. Papa ouvre le panier. Noé s'assoit sur la nappe. Les fesses posées. Maman s'assoit. Ils mangent ensemble, à table. Noé reste assis.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6493,6 +6667,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Noé que fait-il pour manger ?</t>
         </is>
       </c>
     </row>
@@ -6661,6 +6840,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Noé est assis. Après la sieste, à table, ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6849,6 +7033,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -7013,6 +7202,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose le ballon rouge. Il s'assoit. À table, ensemble. Il mange un bout de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7201,6 +7395,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7365,6 +7564,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'assoit. Noé est assis à table, ensemble. Après la sieste. Le ballon est posé.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7527,6 +7731,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7689,6 +7898,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'assoit. Noé reste assis. À table, ensemble. Après la sieste. Il mange du pain.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7851,6 +8065,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8013,6 +8232,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'assoit. Noé est assis à table, ensemble. Après la sieste.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8175,6 +8399,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8337,6 +8566,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose le seau bleu. Il s'assoit. À table, ensemble. Maman tend une serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8525,6 +8759,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8689,6 +8928,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'assoit. Noé est assis à table, ensemble. Maman tend une serviette.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8851,6 +9095,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9013,6 +9262,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'assoit. Noé reste assis. À table, ensemble. Le seau bleu est rangé.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9175,6 +9429,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9337,6 +9596,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sami range le seau. Noé est assis à table, ensemble. Après la sieste.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9499,6 +9763,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9523,7 +9792,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Noé pose le doudou. Il s'assoit. À table, ensemble. Papa dit : on est assis.</t>
+          <t>Noé pose le doudou. Il s'assoit. À table, ensemble. On est assis.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9661,6 +9930,12 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose le doudou. Il s'assoit. À table, ensemble.
+papa|On est assis.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9851,6 +10126,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9875,7 +10155,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Tom s'assoit. Noé est assis à table, ensemble. Papa dit : on est assis.</t>
+          <t>Tom s'assoit. Noé est assis à table, ensemble. On est assis.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10013,6 +10293,12 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'assoit. Noé est assis à table, ensemble.
+papa|On est assis.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10175,6 +10461,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10337,6 +10628,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Léa câline le doudou. Noé reste assis. À table, ensemble. Après la sieste.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10499,6 +10795,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10661,6 +10962,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'assoit près du doudou. Noé est assis à table, ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10823,6 +11129,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10985,6 +11296,11 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, le parc est calme. Papa étend la nappe. Noé s'assoit. Les fesses bien posées. Maman s'assoit. Ils mangent ensemble, à table. Noé reste assis.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11161,6 +11477,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Noé que fait-il pour manger ?</t>
         </is>
       </c>
     </row>
@@ -11329,6 +11650,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Noé est assis. Le soir, à table, ensemble. C'est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11517,6 +11843,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -11681,6 +12012,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose le ballon rouge. Il s'assoit. À table, ensemble. Le ciel est rose.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11869,6 +12205,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12033,6 +12374,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'assoit. Noé est assis à table, ensemble. Le soir. Le ciel est rose.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12195,6 +12541,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12357,6 +12708,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'assoit. Noé reste assis. À table, ensemble. Le soir. La nappe est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12519,6 +12875,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12681,6 +13042,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'assoit. Noé est assis à table, ensemble. Le soir. Le ballon reste.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12843,6 +13209,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13005,6 +13376,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose le seau bleu. Il s'assoit. À table, ensemble. Maman plie un coin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13193,6 +13569,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13357,6 +13738,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'assoit. Noé est assis à table, ensemble. Maman plie un coin.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13519,6 +13905,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13681,6 +14072,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'assoit. Noé reste assis. À table, ensemble. Le soir. Le seau est posé.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13843,6 +14239,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14005,6 +14406,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sami pose le seau. Noé est assis à table, ensemble. Le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14167,6 +14573,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14191,7 +14602,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Noé pose le doudou. Il s'assoit. À table, ensemble. Papa dit : merci d'être assis.</t>
+          <t>Noé pose le doudou. Il s'assoit. À table, ensemble. Merci d'être assis.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14329,6 +14740,12 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose le doudou. Il s'assoit. À table, ensemble.
+papa|Merci d'être assis.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14519,6 +14936,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14543,7 +14965,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Tom s'assoit. Noé est assis à table, ensemble. Le soir. Papa dit : merci d'être assis.</t>
+          <t>Tom s'assoit. Noé est assis à table, ensemble. Le soir. Merci d'être assis.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -14681,6 +15103,12 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Tom s'assoit. Noé est assis à table, ensemble. Le soir.
+papa|Merci d'être assis.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14843,6 +15271,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15005,6 +15438,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Léa tient le doudou. Noé reste assis. À table, ensemble. Le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15167,6 +15605,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15329,6 +15772,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'assoit. Noé est assis à table, ensemble. Le soir. Ils rangent.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15491,6 +15939,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15509,7 +15962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15603,6 +16056,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-020.xlsx
+++ b/stories/arbres/TREE-SAN-020.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,11 @@
           <t>narrateur|Noé va au parc avec papa. Maman porte le panier. C'est l'heure de manger. On s'assoit. Assis à table, ensemble. Ici, la table est une nappe. Noé pose les fesses.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1524,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1692,7 @@
           <t>narrateur|Le matin, l'herbe est fraîche. Papa étend la nappe. Noé s'assoit. Les fesses sur la nappe. Maman s'assoit. Ils mangent ensemble, à table. Noé reste assis.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1864,6 +1876,7 @@
           <t>narrateur|Noé va manger. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2035,6 +2048,7 @@
           <t>narrateur|Noé est assis. Le matin, à table, ensemble. La nappe est leur table.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2230,6 +2244,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2397,6 +2412,7 @@
           <t>narrateur|Noé pose le ballon rouge. Il s'assoit. À table, ensemble. Papa coupe le pain.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2592,6 +2608,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2759,6 +2776,7 @@
           <t>narrateur|Tom s'assoit près de Noé. Ils mangent assis à table, ensemble. Le matin. Le ballon rouge attend.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2926,6 +2944,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3093,6 +3112,7 @@
           <t>narrateur|Léa s'assoit. Noé est assis à table, ensemble. Le matin. Une miette tombe.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3260,6 +3280,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3427,6 +3448,7 @@
           <t>narrateur|Sami s'assoit. Noé reste assis. À table, ensemble. Le matin. Papa coupe le pain.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3594,6 +3616,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3761,6 +3784,7 @@
           <t>narrateur|Noé pose le seau bleu. Il s'assoit. À table, ensemble. Maman verse de l'eau.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3956,6 +3980,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4123,6 +4148,7 @@
           <t>narrateur|Tom s'assoit. Noé est assis à table, ensemble. Le matin. Maman verse de l'eau.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4290,6 +4316,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4457,6 +4484,7 @@
           <t>narrateur|Léa s'assoit tout doux. Noé reste assis. À table, ensemble. Le seau bleu est posé.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4624,6 +4652,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4791,6 +4820,7 @@
           <t>narrateur|Sami pose le seau. Noé est assis à table, ensemble. Le matin, l'herbe est fraîche.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4958,6 +4988,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5126,6 +5157,7 @@
 papa|Bien.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5321,6 +5353,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5488,6 +5521,7 @@
           <t>narrateur|Tom s'assoit. Le doudou aussi, à sa place. Noé est assis à table, ensemble.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5655,6 +5689,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5823,6 +5858,7 @@
 papa|Bien.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5990,6 +6026,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6157,6 +6194,7 @@
           <t>narrateur|Sami tapote le doudou. Noé reste assis. À table, ensemble. Une abeille passe loin.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6324,6 +6362,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6491,6 +6530,7 @@
           <t>narrateur|Après la sieste, Noé a faim. Papa ouvre le panier. Noé s'assoit sur la nappe. Les fesses posées. Maman s'assoit. Ils mangent ensemble, à table. Noé reste assis.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6674,6 +6714,7 @@
           <t>narrateur|Après la sieste, Noé que fait-il pour manger ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6845,6 +6886,7 @@
           <t>narrateur|Noé est assis. Après la sieste, à table, ensemble.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7040,6 +7082,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7207,6 +7250,7 @@
           <t>narrateur|Noé pose le ballon rouge. Il s'assoit. À table, ensemble. Il mange un bout de pain.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7402,6 +7446,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7569,6 +7614,7 @@
           <t>narrateur|Tom s'assoit. Noé est assis à table, ensemble. Après la sieste. Le ballon est posé.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7736,6 +7782,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7903,6 +7950,7 @@
           <t>narrateur|Léa s'assoit. Noé reste assis. À table, ensemble. Après la sieste. Il mange du pain.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8070,6 +8118,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8237,6 +8286,7 @@
           <t>narrateur|Sami s'assoit. Noé est assis à table, ensemble. Après la sieste.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8404,6 +8454,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8571,6 +8622,7 @@
           <t>narrateur|Noé pose le seau bleu. Il s'assoit. À table, ensemble. Maman tend une serviette.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8766,6 +8818,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8933,6 +8986,7 @@
           <t>narrateur|Tom s'assoit. Noé est assis à table, ensemble. Maman tend une serviette.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9100,6 +9154,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9267,6 +9322,7 @@
           <t>narrateur|Léa s'assoit. Noé reste assis. À table, ensemble. Le seau bleu est rangé.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9434,6 +9490,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9601,6 +9658,7 @@
           <t>narrateur|Sami range le seau. Noé est assis à table, ensemble. Après la sieste.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9768,6 +9826,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9936,6 +9995,7 @@
 papa|On est assis.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10131,6 +10191,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10299,6 +10360,7 @@
 papa|On est assis.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10466,6 +10528,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10633,6 +10696,7 @@
           <t>narrateur|Léa câline le doudou. Noé reste assis. À table, ensemble. Après la sieste.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10800,6 +10864,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10967,6 +11032,7 @@
           <t>narrateur|Sami s'assoit près du doudou. Noé est assis à table, ensemble.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11134,6 +11200,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11301,6 +11368,11 @@
           <t>narrateur|Le soir, le parc est calme. Papa étend la nappe. Noé s'assoit. Les fesses bien posées. Maman s'assoit. Ils mangent ensemble, à table. Noé reste assis.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11484,6 +11556,7 @@
           <t>narrateur|Le soir, Noé que fait-il pour manger ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11655,6 +11728,7 @@
           <t>narrateur|Noé est assis. Le soir, à table, ensemble. C'est calme.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11850,6 +11924,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12017,6 +12092,7 @@
           <t>narrateur|Noé pose le ballon rouge. Il s'assoit. À table, ensemble. Le ciel est rose.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12212,6 +12288,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12379,6 +12456,7 @@
           <t>narrateur|Tom s'assoit. Noé est assis à table, ensemble. Le soir. Le ciel est rose.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12546,6 +12624,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12713,6 +12792,7 @@
           <t>narrateur|Léa s'assoit. Noé reste assis. À table, ensemble. Le soir. La nappe est calme.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12880,6 +12960,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13047,6 +13128,7 @@
           <t>narrateur|Sami s'assoit. Noé est assis à table, ensemble. Le soir. Le ballon reste.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13214,6 +13296,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13381,6 +13464,7 @@
           <t>narrateur|Noé pose le seau bleu. Il s'assoit. À table, ensemble. Maman plie un coin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13576,6 +13660,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13743,6 +13828,7 @@
           <t>narrateur|Tom s'assoit. Noé est assis à table, ensemble. Maman plie un coin.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13910,6 +13996,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14077,6 +14164,7 @@
           <t>narrateur|Léa s'assoit. Noé reste assis. À table, ensemble. Le soir. Le seau est posé.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14244,6 +14332,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14411,6 +14500,7 @@
           <t>narrateur|Sami pose le seau. Noé est assis à table, ensemble. Le soir.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14578,6 +14668,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14746,6 +14837,7 @@
 papa|Merci d'être assis.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14941,6 +15033,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15109,6 +15202,7 @@
 papa|Merci d'être assis.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15276,6 +15370,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15443,6 +15538,7 @@
           <t>narrateur|Léa tient le doudou. Noé reste assis. À table, ensemble. Le soir.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15610,6 +15706,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15777,6 +15874,7 @@
           <t>narrateur|Sami s'assoit. Noé est assis à table, ensemble. Le soir. Ils rangent.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15944,6 +16042,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15962,7 +16061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16063,6 +16162,20 @@
       <c r="A14" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16264,6 +16377,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
